--- a/samples/product_bulk_upload_sample.xlsx
+++ b/samples/product_bulk_upload_sample.xlsx
@@ -397,18 +397,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:L6"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,193 +421,229 @@
         <v>Item Description</v>
       </c>
       <c r="C1" t="str">
+        <v>Vendor Code</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Design Code</v>
+      </c>
+      <c r="E1" t="str">
+        <v>HSN Code</v>
+      </c>
+      <c r="F1" t="str">
         <v>Retail Price</v>
       </c>
-      <c r="D1" t="str">
-        <v>Discount</v>
-      </c>
-      <c r="E1" t="str">
-        <v>GST %</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Quantity</v>
-      </c>
       <c r="G1" t="str">
-        <v>Low Stock Threshold</v>
+        <v>Before Discount</v>
       </c>
       <c r="H1" t="str">
-        <v>Vendor</v>
+        <v>GST</v>
       </c>
       <c r="I1" t="str">
-        <v>HSN</v>
+        <v>Base UOM</v>
       </c>
       <c r="J1" t="str">
-        <v>Design Code</v>
+        <v>Closing Bal.Qty</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Sub Category</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>STK-BULK-001</v>
+        <v>PK003918</v>
       </c>
       <c r="B2" t="str">
-        <v>Kanchipuram Silk Saree</v>
-      </c>
-      <c r="C2">
-        <v>4500</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
+        <v>Narayanpet</v>
+      </c>
+      <c r="C2" t="str">
+        <v>PK</v>
+      </c>
+      <c r="D2" t="str">
+        <v>9999</v>
+      </c>
+      <c r="E2" t="str">
+        <v>5208</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>1500</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>1800</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>5.00%</v>
       </c>
       <c r="I2" t="str">
-        <v>5007</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
+        <v>Each</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="str">
+        <v>PK</v>
+      </c>
+      <c r="L2" t="str">
+        <v>9999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>STK-BULK-002</v>
+        <v>PK003919</v>
       </c>
       <c r="B3" t="str">
-        <v>Chettinad Cotton Saree</v>
-      </c>
-      <c r="C3">
-        <v>1800</v>
-      </c>
-      <c r="D3">
-        <v>100</v>
-      </c>
-      <c r="E3">
+        <v>Kanchipuram Silk</v>
+      </c>
+      <c r="C3" t="str">
+        <v>PK</v>
+      </c>
+      <c r="D3" t="str">
+        <v>9999</v>
+      </c>
+      <c r="E3" t="str">
+        <v>5007</v>
+      </c>
+      <c r="F3">
+        <v>4500</v>
+      </c>
+      <c r="G3">
+        <v>5000</v>
+      </c>
+      <c r="H3" t="str">
+        <v>12.00%</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Each</v>
+      </c>
+      <c r="J3">
         <v>5</v>
       </c>
-      <c r="F3">
-        <v>25</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>5208</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
+      <c r="K3" t="str">
+        <v>PK</v>
+      </c>
+      <c r="L3" t="str">
+        <v>9999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>STK-BULK-003</v>
+        <v>PK003920</v>
       </c>
       <c r="B4" t="str">
-        <v>Temple Border Silk Saree</v>
-      </c>
-      <c r="C4">
-        <v>6200</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>12</v>
+        <v>Chettinad Cotton</v>
+      </c>
+      <c r="C4" t="str">
+        <v>PK</v>
+      </c>
+      <c r="D4" t="str">
+        <v>9999</v>
+      </c>
+      <c r="E4" t="str">
+        <v>5208</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>1800</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2000</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>5.00%</v>
       </c>
       <c r="I4" t="str">
-        <v>5007</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
+        <v>Each</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4" t="str">
+        <v>PK</v>
+      </c>
+      <c r="L4" t="str">
+        <v>9999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>STK-BULK-004</v>
+        <v>PK003921</v>
       </c>
       <c r="B5" t="str">
-        <v>Handloom Linen Saree</v>
-      </c>
-      <c r="C5">
-        <v>3200</v>
-      </c>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
+        <v>Temple Border Silk</v>
+      </c>
+      <c r="C5" t="str">
+        <v>PK</v>
+      </c>
+      <c r="D5" t="str">
+        <v>9999</v>
+      </c>
+      <c r="E5" t="str">
+        <v>5007</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>6200</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>6500</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>12.00%</v>
       </c>
       <c r="I5" t="str">
-        <v>5309</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
+        <v>Each</v>
+      </c>
+      <c r="J5">
+        <v>8</v>
+      </c>
+      <c r="K5" t="str">
+        <v>PK</v>
+      </c>
+      <c r="L5" t="str">
+        <v>9999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>STK-BULK-005</v>
+        <v>PK003922</v>
       </c>
       <c r="B6" t="str">
-        <v>Bridal Silk Saree</v>
-      </c>
-      <c r="C6">
-        <v>12500</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
+        <v>Handloom Linen</v>
+      </c>
+      <c r="C6" t="str">
+        <v>PK</v>
+      </c>
+      <c r="D6" t="str">
+        <v>9999</v>
+      </c>
+      <c r="E6" t="str">
+        <v>5309</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>3200</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3500</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>5.00%</v>
       </c>
       <c r="I6" t="str">
-        <v>5007</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
+        <v>Each</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6" t="str">
+        <v>PK</v>
+      </c>
+      <c r="L6" t="str">
+        <v>9999</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>